--- a/table_from_link/29274321_table1.xlsx
+++ b/table_from_link/29274321_table1.xlsx
@@ -472,11 +472,7 @@
           <t>Closest Genes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
+      <c r="L1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -486,14 +482,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aβ42</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20647323</v>
+          <t>Aβ 42</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20647323</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,20 +505,24 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.16</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0.07000000000000001</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.54×10−8</t>
+          <t>2.54×10 −8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -550,14 +554,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aβ42</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="n">
-        <v>13870464</v>
+          <t>Aβ 42</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13870464</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -569,20 +577,24 @@
           <t>G</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0.07000000000000001</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>−1.02</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0.18</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.53×10−8</t>
+          <t>2.53×10 −8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -600,14 +612,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aβ42</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D5" t="n">
-        <v>59687842</v>
+          <t>Aβ 42</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>59687842</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -619,20 +635,24 @@
           <t>T</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0.44</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>−0.53</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0.1</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.03×10−8</t>
+          <t>2.03×10 −8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -671,11 +691,15 @@
           <t>t-Tau</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" t="n">
-        <v>119390525</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>119390525</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -687,20 +711,24 @@
           <t>T</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.34</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0.09</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.59×10−9</t>
+          <t>1.59×10 −9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -721,11 +749,15 @@
           <t>t-Tau</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>105385352</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>105385352</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -737,20 +769,24 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0.13</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>−0.80</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.14</v>
+          <t>− 0.80</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.94×10−9</t>
+          <t>6.94×10 −9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -789,11 +825,15 @@
           <t>HPV</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>17496561</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>17496561</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -805,20 +845,24 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0.12</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0.1</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.58×10−9</t>
+          <t>4.58×10 −9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -857,11 +901,15 @@
           <t>LMdT</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>57739164</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>57739164</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -873,20 +921,24 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0.03</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0.14</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.30×10−8</t>
+          <t>4.30×10 −8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -907,11 +959,15 @@
           <t>LMdT</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" t="n">
-        <v>53818149</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>53818149</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -923,20 +979,24 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.21</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0.05</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.01×10−8</t>
+          <t>2.01×10 −8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -971,11 +1031,15 @@
           <t>LMdT</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>86416554</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>86416554</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -987,20 +1051,24 @@
           <t>G</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0.02</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>−0.93</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0.17</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.74×10−8</t>
+          <t>2.74×10 −8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1021,11 +1089,15 @@
           <t>LMdT</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>88406552</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>88406552</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1037,20 +1109,24 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.02</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>−0.84</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.14</v>
+          <t>− 0.84</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.86×10−9</t>
+          <t>2.86×10 −9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1089,11 +1165,15 @@
           <t>LMiT</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>31228770</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>31228770</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1105,20 +1185,24 @@
           <t>G</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0.04</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>−0.61</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0.11</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.72×10−8</t>
+          <t>1.72×10 −8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1153,11 +1237,15 @@
           <t>HPV</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>136077929</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>136077929</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1169,20 +1257,24 @@
           <t>T</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0.02</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0.31</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.76×10−8</t>
+          <t>1.76×10 −8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
